--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N12_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N12_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>76.42828485031521</v>
+        <v>12.41959628817622</v>
       </c>
       <c r="D2" t="n">
-        <v>67.15657775809004</v>
+        <v>10.91294388568963</v>
       </c>
       <c r="E2" t="n">
-        <v>17.35870413759136</v>
+        <v>2.820789422358595</v>
       </c>
       <c r="F2" t="n">
-        <v>16.21478736580812</v>
+        <v>2.634902946943819</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>22.50703069331339</v>
+        <v>3.657392487663426</v>
       </c>
       <c r="D3" t="n">
-        <v>22.20360331117452</v>
+        <v>3.608085538065859</v>
       </c>
       <c r="E3" t="n">
-        <v>17.35870413759136</v>
+        <v>2.820789422358595</v>
       </c>
       <c r="F3" t="n">
-        <v>16.21478736580812</v>
+        <v>2.634902946943819</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>60.06430696309481</v>
+        <v>9.760449881502906</v>
       </c>
       <c r="D4" t="n">
-        <v>48.27007354458868</v>
+        <v>7.843886950995661</v>
       </c>
       <c r="E4" t="n">
-        <v>17.35870413759136</v>
+        <v>2.820789422358595</v>
       </c>
       <c r="F4" t="n">
-        <v>16.21478736580812</v>
+        <v>2.634902946943819</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.0064713304389</v>
+        <v>3.413551591196321</v>
       </c>
       <c r="D5" t="n">
-        <v>23.30549538109992</v>
+        <v>3.787142999428738</v>
       </c>
       <c r="E5" t="n">
-        <v>17.35870413759136</v>
+        <v>2.820789422358595</v>
       </c>
       <c r="F5" t="n">
-        <v>16.21478736580812</v>
+        <v>2.634902946943819</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>45.55012876743302</v>
+        <v>7.401895924707866</v>
       </c>
       <c r="D6" t="n">
-        <v>47.73732947867434</v>
+        <v>7.75731604028458</v>
       </c>
       <c r="E6" t="n">
-        <v>17.35870413759136</v>
+        <v>2.820789422358595</v>
       </c>
       <c r="F6" t="n">
-        <v>16.21478736580812</v>
+        <v>2.634902946943819</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>21.37587850406123</v>
+        <v>3.47358025690995</v>
       </c>
       <c r="D7" t="n">
-        <v>18.17399926743469</v>
+        <v>2.953274880958138</v>
       </c>
       <c r="E7" t="n">
-        <v>17.35870413759136</v>
+        <v>2.820789422358595</v>
       </c>
       <c r="F7" t="n">
-        <v>16.21478736580812</v>
+        <v>2.634902946943819</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>12.89028696218941</v>
+        <v>2.09467163135578</v>
       </c>
       <c r="D8" t="n">
-        <v>10.06932742402874</v>
+        <v>1.636265706404671</v>
       </c>
       <c r="E8" t="n">
-        <v>17.35870413759136</v>
+        <v>2.820789422358595</v>
       </c>
       <c r="F8" t="n">
-        <v>16.21478736580812</v>
+        <v>2.634902946943819</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>30.17412568658483</v>
+        <v>4.903295424070034</v>
       </c>
       <c r="D9" t="n">
-        <v>33.78748235453038</v>
+        <v>5.490465882611187</v>
       </c>
       <c r="E9" t="n">
-        <v>17.35870413759136</v>
+        <v>2.820789422358595</v>
       </c>
       <c r="F9" t="n">
-        <v>16.21478736580812</v>
+        <v>2.634902946943819</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>35.11495186903744</v>
+        <v>5.706179678718584</v>
       </c>
       <c r="D10" t="n">
-        <v>36.95720322584209</v>
+        <v>6.00554552419934</v>
       </c>
       <c r="E10" t="n">
-        <v>17.35870413759136</v>
+        <v>2.820789422358595</v>
       </c>
       <c r="F10" t="n">
-        <v>16.21478736580812</v>
+        <v>2.634902946943819</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>21.4304154912013</v>
+        <v>3.482442517320212</v>
       </c>
       <c r="D11" t="n">
-        <v>14.1598022585063</v>
+        <v>2.300967867007273</v>
       </c>
       <c r="E11" t="n">
-        <v>17.35870413759136</v>
+        <v>2.820789422358595</v>
       </c>
       <c r="F11" t="n">
-        <v>16.21478736580812</v>
+        <v>2.634902946943819</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>15.21847591164064</v>
+        <v>2.473002335641604</v>
       </c>
       <c r="D12" t="n">
-        <v>12.86737272756336</v>
+        <v>2.090948068229046</v>
       </c>
       <c r="E12" t="n">
-        <v>17.35870413759136</v>
+        <v>2.820789422358595</v>
       </c>
       <c r="F12" t="n">
-        <v>16.21478736580812</v>
+        <v>2.634902946943819</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>4.943403862283566</v>
+        <v>0.8033031276210796</v>
       </c>
       <c r="D13" t="n">
-        <v>12.56870540619004</v>
+        <v>2.042414628505882</v>
       </c>
       <c r="E13" t="n">
-        <v>17.35870413759136</v>
+        <v>2.820789422358595</v>
       </c>
       <c r="F13" t="n">
-        <v>16.21478736580812</v>
+        <v>2.634902946943819</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>23.42426166792534</v>
+        <v>3.806442521037867</v>
       </c>
       <c r="D14" t="n">
-        <v>26.45169040797109</v>
+        <v>4.298399691295303</v>
       </c>
       <c r="E14" t="n">
-        <v>17.35870413759136</v>
+        <v>2.820789422358595</v>
       </c>
       <c r="F14" t="n">
-        <v>16.21478736580812</v>
+        <v>2.634902946943819</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>11.72111517604327</v>
+        <v>1.904681216107031</v>
       </c>
       <c r="D15" t="n">
-        <v>6.574060089677078</v>
+        <v>1.068284764572525</v>
       </c>
       <c r="E15" t="n">
-        <v>17.35870413759136</v>
+        <v>2.820789422358595</v>
       </c>
       <c r="F15" t="n">
-        <v>16.21478736580812</v>
+        <v>2.634902946943819</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>9.082887153842574</v>
+        <v>1.475969162499418</v>
       </c>
       <c r="D16" t="n">
-        <v>5.903130626686541</v>
+        <v>0.9592587268365629</v>
       </c>
       <c r="E16" t="n">
-        <v>17.35870413759136</v>
+        <v>2.820789422358595</v>
       </c>
       <c r="F16" t="n">
-        <v>16.21478736580812</v>
+        <v>2.634902946943819</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>19.02850153072251</v>
+        <v>3.092131498742408</v>
       </c>
       <c r="D17" t="n">
-        <v>7.772508294861219</v>
+        <v>1.263032597914948</v>
       </c>
       <c r="E17" t="n">
-        <v>17.35870413759136</v>
+        <v>2.820789422358595</v>
       </c>
       <c r="F17" t="n">
-        <v>16.21478736580812</v>
+        <v>2.634902946943819</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>1.000342144517895</v>
+        <v>0.162555598484158</v>
       </c>
       <c r="D18" t="n">
-        <v>1.698929941985332</v>
+        <v>0.2760761155726165</v>
       </c>
       <c r="E18" t="n">
-        <v>17.35870413759136</v>
+        <v>2.820789422358595</v>
       </c>
       <c r="F18" t="n">
-        <v>16.21478736580812</v>
+        <v>2.634902946943819</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>26.33038432933448</v>
+        <v>4.278687453516853</v>
       </c>
       <c r="D19" t="n">
-        <v>16.39971988496078</v>
+        <v>2.664954481306126</v>
       </c>
       <c r="E19" t="n">
-        <v>17.35870413759136</v>
+        <v>2.820789422358595</v>
       </c>
       <c r="F19" t="n">
-        <v>16.21478736580812</v>
+        <v>2.634902946943819</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>16.48830457800056</v>
+        <v>2.679349493925092</v>
       </c>
       <c r="D20" t="n">
-        <v>17.03405940471228</v>
+        <v>2.768034653265745</v>
       </c>
       <c r="E20" t="n">
-        <v>17.35870413759136</v>
+        <v>2.820789422358595</v>
       </c>
       <c r="F20" t="n">
-        <v>16.21478736580812</v>
+        <v>2.634902946943819</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>33.69523809240526</v>
+        <v>5.475476190015855</v>
       </c>
       <c r="D21" t="n">
-        <v>23.29622858948717</v>
+        <v>3.785637145791665</v>
       </c>
       <c r="E21" t="n">
-        <v>17.35870413759136</v>
+        <v>2.820789422358595</v>
       </c>
       <c r="F21" t="n">
-        <v>16.21478736580812</v>
+        <v>2.634902946943819</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>20.9568051672526</v>
+        <v>3.405480839678547</v>
       </c>
       <c r="D22" t="n">
-        <v>8.384622476327879</v>
+        <v>1.36250115240328</v>
       </c>
       <c r="E22" t="n">
-        <v>17.35870413759136</v>
+        <v>2.820789422358595</v>
       </c>
       <c r="F22" t="n">
-        <v>16.21478736580812</v>
+        <v>2.634902946943819</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
